--- a/data_extactor/batch_10_fa/trimmed/batch_0085_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0085_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | تولید مواد غذایی | تولید و فراوری | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | تولید مواد غذایی | تولید و فرآوری | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | چابکی انگشتان | چابکی دستی | دید نزدیک | استحکام تنه | قدرت ایستا | دقت کنترل</t>
+          <t>ثبات دست و بازو | مهارت انگشتان | مهارت دستی | بینایی نزدیک | قدرت تنه | قدرت ایستا | دقت کنترل</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>پرورش‌دهندگان دام و طیور | قصابان و قطعه‌کاران گوشت | کارگران مزارع پرورش دام، طیور و آبزیان | تولیدکنندگان فرمولی و دسته‌ای مواد غذایی | کارگران آماده‌سازی غذا | قطعه‌کاران و پاک‌کنندگان گوشت، مرغ و ماهی | کارگران دستی بسته‌بندی</t>
+          <t>تکنسین‌ها و کارشناسان اصلاح نژاد و پرورش دام | قصابان و برش‌کاران گوشت | کارگران پرورش دام، طیور و آبزیان | تولیدکنندگان فرمولی و دسته‌ای مواد غذایی | کارگران آماده‌سازی غذا | برش‌کاران و پاک‌کنندگان گوشت، مرغ و آبزیان | کارگران بسته‌بندی دستی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,22 +560,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Microsoft Excel | نرم‌افزار ایمیل</t>
+          <t>نرم‌افزار ایمیل</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | درک مطلب | شنیدن فعال | سخن گفتن</t>
+          <t>نظارت | تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>تولید و فراوری | زبان انگلیسی | ایمنی و امنیت عمومی | تولید مواد غذایی</t>
+          <t>تولید و فرآوری | زبان انگلیسی | ایمنی و امنیت عمومی | تولید مواد غذایی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>دید نزدیک | حساسیت به مسئله | دقت کنترل | ثبات دست و بازو | توجه انتخابی | تشخیص تمایز رنگ‌ها | کنترل نرخ فرایند</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | دقت کنترل | ثبات دست و بازو | توجه انتخابی | تشخیص رنگ بصری | کنترل نرخ</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>نانوایان و شیرینی‌پزان | تنظیم‌کنندگان و اپراتورهای ماشین‌های خردایش، آسیاب و پرداخت | تولیدکنندگان فرمولی و دسته‌ای مواد غذایی | اپراتورهای ماشین‌آلات پخت مواد غذایی | اپراتورهای کوره‌ها، خشک‌کن‌ها و دیگ‌های پخت | تنظیم‌کنندگان و اپراتورهای ماشین‌های ترکیب و مخلوط‌کن مواد | اپراتورهای ماشین‌های بسته‌بندی و پرکن</t>
+          <t>نانوایان و شیرینی‌پزان | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تولیدکنندگان فرمولی و دسته‌ای مواد غذایی | اپراتورهای ماشین‌آلات پخت مواد غذایی | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌های صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های مخلوط‌کن و ترکیب مواد | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,22 +617,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Microsoft Office | نرم‌افزار Plex Manufacturing Cloud | نرم‌افزار تخصصی Edible Software</t>
+          <t>Microsoft Office | نرم‌افزار Microsoft Office | نرم‌افزار تخصصی Edible Software</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | سخن گفتن | شنیدن فعال</t>
+          <t>درک مطلب | تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | تولید مواد غذایی | تولید و فراوری | مکانیک | مدیریت و امور اداری | ریاضیات</t>
+          <t>ایمنی و امنیت عمومی | تولید مواد غذایی | تولید و فرآوری | مکانیک | مدیریت و اداره | ریاضیات</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>مرتب‌سازی اطلاعات | دید نزدیک | درک شفاهی | دقت کنترل | حساسیت به مسئله | درک کتبی | انعطاف‌پذیری طبقه‌بندی</t>
+          <t>ترتیب‌دهی اطلاعات | بینایی نزدیک | درک شفاهی | دقت کنترل | حساسیت به مسئله | درک کتبی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>نانوایان و شیرینی‌پزان | تنظیم‌کنندگان و اپراتورهای ماشین‌های خردایش، آسیاب و پرداخت | اپراتورهای ماشین‌آلات پخت مواد غذایی | اپراتورهای ماشین‌های برشته‌کاری، پخت و خشک‌کن مواد غذایی و توتون | اپراتورهای کوره‌ها، خشک‌کن‌ها و دیگ‌های پخت | تنظیم‌کنندگان و اپراتورهای ماشین‌های ترکیب و مخلوط‌کن مواد | اپراتورهای ماشین‌های بسته‌بندی و پرکن</t>
+          <t>نانوایان و شیرینی‌پزان | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | اپراتورهای ماشین‌آلات پخت مواد غذایی | اپراتورهای ماشین‌آلات برشته‌کاری، پخت و خشک‌کن مواد غذایی و توتون | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌های صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های مخلوط‌کن و ترکیب مواد | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | نظارت | تفکر انتقادی | شنیدن فعال</t>
+          <t>درک مطلب | نظارت | تفکر انتقادی | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>تولید و فراوری | تولید مواد غذایی | مدیریت و امور اداری | آموزش و تعلیم | مکانیک</t>
+          <t>تولید و فرآوری | تولید مواد غذایی | مدیریت و اداره | آموزش و پرورش | مکانیک</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک کتبی | درک شفاهی | دید نزدیک | دقت کنترل | توجه انتخابی | مرتب‌سازی اطلاعات</t>
+          <t>حساسیت به مسئله | درک کتبی | درک شفاهی | بینایی نزدیک | دقت کنترل | توجه انتخابی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>نانوایان و شیرینی‌پزان | آشپزهای رستوران | تولیدکنندگان فرمولی و دسته‌ای مواد غذایی | اپراتورهای ماشین‌های برشته‌کاری، پخت و خشک‌کن مواد غذایی و توتون | اپراتورهای کوره‌ها، خشک‌کن‌ها و دیگ‌های پخت | تنظیم‌کنندگان و اپراتورهای ماشین‌های ترکیب و مخلوط‌کن مواد | اپراتورهای ماشین‌های بسته‌بندی و پرکن</t>
+          <t>نانوایان و شیرینی‌پزان | آشپزان رستوران | تولیدکنندگان فرمولی و دسته‌ای مواد غذایی | اپراتورهای ماشین‌آلات برشته‌کاری، پخت و خشک‌کن مواد غذایی و توتون | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌های صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های مخلوط‌کن و ترکیب مواد | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>تولید مواد غذایی | تولید و فراوری | زبان انگلیسی | شیمی | مکانیک | ایمنی و امنیت عمومی | ریاضیات</t>
+          <t>تولید مواد غذایی | تولید و فرآوری | زبان انگلیسی | شیمی | مکانیک | ایمنی و امنیت عمومی | ریاضیات</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | ثبات دست و بازو | هماهنگی چند اندام | دقت کنترل | قدرت ایستا | دید نزدیک</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>تولیدکنندگان فرمولی و دسته‌ای مواد غذایی | نانوایان و شیرینی‌پزان | قطعه‌کاران و پاک‌کنندگان گوشت، مرغ و ماهی | اپراتورهای ماشین‌آلات پخت مواد غذایی | اپراتورهای ماشین‌های بسته‌بندی و پرکن | درجه‌بندی‌کنندگان و سورت‌کنندگان محصولات کشاورزی | کارگران دستی بسته‌بندی</t>
+          <t>تولیدکنندگان فرمولی و دسته‌ای مواد غذایی | نانوایان و شیرینی‌پزان | برش‌کاران و پاک‌کنندگان گوشت، مرغ و آبزیان | اپراتورهای ماشین‌آلات پخت مواد غذایی | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | کارگران درجه‌بندی و تفکیک محصولات کشاورزی | کارگران بسته‌بندی دستی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>تولید و فراوری | ریاضیات | زبان انگلیسی</t>
+          <t>تولید و فرآوری | ریاضیات | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>دقت کنترل | هماهنگی چند اندام | چابکی دستی | حساسیت به مسئله | دید نزدیک | کنترل نرخ فرایند | ثبات دست و بازو</t>
+          <t>دقت کنترل | هماهنگی چند عضو | مهارت دستی | حساسیت به مسئله | بینایی نزدیک | کنترل نرخ | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن، شکل‌دهی و پرس مواد | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای تراشکاری فلز و پلاستیک | کارگران بارگیری و تغذیه خطوط تولید | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک</t>
+          <t>تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,22 +845,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>نرم‌افزار کنترل دستگاه | نرم‌افزار ردیابی موجودی انبار | نرم‌افزار ایمیل</t>
+          <t>نرم‌افزار ایمیل | نرم‌افزار ردیابی موجودی انبار</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>نظارت | درک مطلب | شنیدن فعال</t>
+          <t>نظارت | درک مطلب | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>تولید و فراوری | ریاضیات | آموزش و تعلیم | مکانیک | مهندسی و فناوری | طراحی</t>
+          <t>تولید و فرآوری | ریاضیات | آموزش و پرورش | مکانیک | مهندسی و فناوری | طراحی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | ثبات دست و بازو | دقت کنترل | زمان واکنش | چابکی دستی</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | ثبات دست و بازو | دقت کنترل | زمان عکس‌العمل | مهارت دستی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای تراشکاری فلز و پلاستیک | کارگران بارگیری و تغذیه خطوط تولید | تنظیم‌کنندگان و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک</t>
+          <t>تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,22 +902,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>نرم‌افزار مرورگر وب | نرم‌افزار ایمیل</t>
+          <t>نرم‌افزار ایمیل | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>نظارت | سخن گفتن | شنیدن فعال | تفکر انتقادی | یادگیری فعال | درک مطلب</t>
+          <t>نظارت | سخن گفتن | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>مکانیک | تولید و فراوری | زبان انگلیسی | آموزش و تعلیم</t>
+          <t>مکانیک | تولید و فرآوری | زبان انگلیسی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | دقت کنترل | زمان واکنش | دید نزدیک | کنترل نرخ فرایند | چابکی دستی | ثبات دست و بازو</t>
+          <t>حساسیت به مسئله | دقت کنترل | زمان عکس‌العمل | بینایی نزدیک | کنترل نرخ | مهارت دستی | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای تراشکاری فلز و پلاستیک | کارگران بارگیری و تغذیه خطوط تولید | تنظیم‌کنندگان و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک</t>
+          <t>تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نظارت | تفکر انتقادی | سخن گفتن</t>
+          <t>گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>تولید و فراوری</t>
+          <t>تولید و فرآوری</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | دقت کنترل | دید نزدیک | مرتب‌سازی اطلاعات | چابکی دستی | زمان واکنش | توجه انتخابی</t>
+          <t>ثبات دست و بازو | دقت کنترل | بینایی نزدیک | ترتیب‌دهی اطلاعات | مهارت دستی | زمان عکس‌العمل | توجه انتخابی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای سوراخ‌کاری و حفاری فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای تراشکاری فلز و پلاستیک | کارگران بارگیری و تغذیه خطوط تولید | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک</t>
+          <t>تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای سوراخ‌کاری و حفاری فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,22 +1016,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>نرم‌افزار کنترل عددی رایانه‌ای CNC | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | نرم‌افزار SAP | نرم‌افزار انبارداری خودکار</t>
+          <t>نرم‌افزار خودکار موجودی | Microsoft Excel | نرم‌افزار Microsoft Office | نرم‌افزار SAP</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | نظارت | تفکر انتقادی | سخن گفتن | شنیدن فعال</t>
+          <t>درک مطلب | نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ریاضیات | تولید و فراوری | مکانیک | مهندسی و فناوری | طراحی | مدیریت و امور اداری</t>
+          <t>ریاضیات | تولید و فرآوری | مکانیک | مهندسی و فناوری | طراحی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>دقت کنترل | دید نزدیک | ثبات دست و بازو | حساسیت به مسئله | مرتب‌سازی اطلاعات | چابکی دستی | تجسم فضایی</t>
+          <t>دقت کنترل | بینایی نزدیک | ثبات دست و بازو | حساسیت به مسئله | ترتیب‌دهی اطلاعات | مهارت دستی | تجسم</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>اپراتورهای ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای سنگ‌زنی، لپینگ، پرداخت و بافینگ فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای تراشکاری فلز و پلاستیک | ماشین‌کاران صنعتی | تنظیم‌کنندگان و اپراتورهای ماشین‌های فرز و صفحه تراش فلز و پلاستیک</t>
+          <t>اپراتورهای ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
